--- a/NSE_FNO_Technical_Metrics.xlsx
+++ b/NSE_FNO_Technical_Metrics.xlsx
@@ -2060,7 +2060,7 @@
         <v>57</v>
       </c>
       <c r="P2">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="Q2">
         <v>1054.32</v>
@@ -2176,7 +2176,7 @@
         <v>87</v>
       </c>
       <c r="P3">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="Q3">
         <v>6914.5</v>
@@ -2292,7 +2292,7 @@
         <v>83</v>
       </c>
       <c r="P4">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="Q4">
         <v>375.55</v>
@@ -2408,7 +2408,7 @@
         <v>77</v>
       </c>
       <c r="P5">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="Q5">
         <v>1307.16</v>
@@ -2524,7 +2524,7 @@
         <v>45</v>
       </c>
       <c r="P6">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="Q6">
         <v>2737.46</v>
@@ -2640,7 +2640,7 @@
         <v>67</v>
       </c>
       <c r="P7">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="Q7">
         <v>1285.98</v>
@@ -2756,7 +2756,7 @@
         <v>86</v>
       </c>
       <c r="P8">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="Q8">
         <v>1755.3</v>
@@ -2872,7 +2872,7 @@
         <v>75</v>
       </c>
       <c r="P9">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="Q9">
         <v>195.47</v>
@@ -3104,7 +3104,7 @@
         <v>18</v>
       </c>
       <c r="P11">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="Q11">
         <v>6675.8</v>
@@ -3220,7 +3220,7 @@
         <v>6</v>
       </c>
       <c r="P12">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="Q12">
         <v>355.49</v>
@@ -3452,7 +3452,7 @@
         <v>92</v>
       </c>
       <c r="P14">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="Q14">
         <v>2108.18</v>
@@ -3568,7 +3568,7 @@
         <v>59</v>
       </c>
       <c r="P15">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="Q15">
         <v>7902</v>
@@ -3684,7 +3684,7 @@
         <v>61</v>
       </c>
       <c r="P16">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="Q16">
         <v>149.12</v>
@@ -3800,7 +3800,7 @@
         <v>49</v>
       </c>
       <c r="P17">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="Q17">
         <v>2362.6</v>
@@ -3916,7 +3916,7 @@
         <v>73</v>
       </c>
       <c r="P18">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="Q18">
         <v>1402.08</v>
@@ -4032,7 +4032,7 @@
         <v>83</v>
       </c>
       <c r="P19">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="Q19">
         <v>1001.52</v>
@@ -4148,7 +4148,7 @@
         <v>96</v>
       </c>
       <c r="P20">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="Q20">
         <v>1677.54</v>
@@ -4264,7 +4264,7 @@
         <v>69</v>
       </c>
       <c r="P21">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="Q21">
         <v>1243.36</v>
@@ -4496,7 +4496,7 @@
         <v>33</v>
       </c>
       <c r="P23">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q23">
         <v>1737.96</v>
@@ -4612,7 +4612,7 @@
         <v>60</v>
       </c>
       <c r="P24">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="Q24">
         <v>10682.8</v>
@@ -4728,7 +4728,7 @@
         <v>50</v>
       </c>
       <c r="P25">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="Q25">
         <v>962.58</v>
@@ -4844,7 +4844,7 @@
         <v>29</v>
       </c>
       <c r="P26">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="Q26">
         <v>161.59</v>
@@ -4960,7 +4960,7 @@
         <v>50</v>
       </c>
       <c r="P27">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="Q27">
         <v>233.98</v>
@@ -5076,7 +5076,7 @@
         <v>70</v>
       </c>
       <c r="P28">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="Q28">
         <v>133.2</v>
@@ -5192,7 +5192,7 @@
         <v>9</v>
       </c>
       <c r="P29">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="Q29">
         <v>1081.88</v>
@@ -5308,7 +5308,7 @@
         <v>35</v>
       </c>
       <c r="P30">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="Q30">
         <v>377.2</v>
@@ -5424,7 +5424,7 @@
         <v>89</v>
       </c>
       <c r="P31">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q31">
         <v>1832.46</v>
@@ -5656,7 +5656,7 @@
         <v>97</v>
       </c>
       <c r="P33">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="Q33">
         <v>438.54</v>
@@ -5772,7 +5772,7 @@
         <v>44</v>
       </c>
       <c r="P34">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="Q34">
         <v>359.66</v>
@@ -5888,7 +5888,7 @@
         <v>47</v>
       </c>
       <c r="P35">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="Q35">
         <v>1540.92</v>
@@ -6004,7 +6004,7 @@
         <v>80</v>
       </c>
       <c r="P36">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="Q36">
         <v>44214</v>
@@ -6120,7 +6120,7 @@
         <v>43</v>
       </c>
       <c r="P37">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="Q37">
         <v>293.57</v>
@@ -6236,7 +6236,7 @@
         <v>31</v>
       </c>
       <c r="P38">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="Q38">
         <v>4800.88</v>
@@ -6352,7 +6352,7 @@
         <v>91</v>
       </c>
       <c r="P39">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="Q39">
         <v>3292.52</v>
@@ -6468,7 +6468,7 @@
         <v>32</v>
       </c>
       <c r="P40">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="Q40">
         <v>681.47</v>
@@ -6584,7 +6584,7 @@
         <v>54</v>
       </c>
       <c r="P41">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="Q41">
         <v>118.48</v>
@@ -6816,7 +6816,7 @@
         <v>73</v>
       </c>
       <c r="P43">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="Q43">
         <v>881.28</v>
@@ -6932,7 +6932,7 @@
         <v>44</v>
       </c>
       <c r="P44">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="Q44">
         <v>1582.54</v>
@@ -7048,7 +7048,7 @@
         <v>37</v>
       </c>
       <c r="P45">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="Q45">
         <v>1322.14</v>
@@ -7164,7 +7164,7 @@
         <v>76</v>
       </c>
       <c r="P46">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="Q46">
         <v>414.43</v>
@@ -7280,7 +7280,7 @@
         <v>10</v>
       </c>
       <c r="P47">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="Q47">
         <v>1250.18</v>
@@ -7396,7 +7396,7 @@
         <v>92</v>
       </c>
       <c r="P48">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Q48">
         <v>1841.22</v>
@@ -7512,7 +7512,7 @@
         <v>34</v>
       </c>
       <c r="P49">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="Q49">
         <v>1779.06</v>
@@ -7628,7 +7628,7 @@
         <v>36</v>
       </c>
       <c r="P50">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="Q50">
         <v>440.61</v>
@@ -7860,7 +7860,7 @@
         <v>76</v>
       </c>
       <c r="P52">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="Q52">
         <v>4838.88</v>
@@ -7976,7 +7976,7 @@
         <v>30</v>
       </c>
       <c r="P53">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="Q53">
         <v>382.92</v>
@@ -8092,7 +8092,7 @@
         <v>20</v>
       </c>
       <c r="P54">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="Q54">
         <v>1637.58</v>
@@ -8208,7 +8208,7 @@
         <v>20</v>
       </c>
       <c r="P55">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="Q55">
         <v>400.69</v>
@@ -8556,7 +8556,7 @@
         <v>45</v>
       </c>
       <c r="P58">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="Q58">
         <v>656.13</v>
@@ -8672,7 +8672,7 @@
         <v>27</v>
       </c>
       <c r="P59">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="Q59">
         <v>3577.34</v>
@@ -8788,7 +8788,7 @@
         <v>62</v>
       </c>
       <c r="P60">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="Q60">
         <v>1198.36</v>
@@ -8904,7 +8904,7 @@
         <v>61</v>
       </c>
       <c r="P61">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="Q61">
         <v>6970</v>
@@ -9020,7 +9020,7 @@
         <v>78</v>
       </c>
       <c r="P62">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="Q62">
         <v>324.06</v>
@@ -9252,7 +9252,7 @@
         <v>97</v>
       </c>
       <c r="P64">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="Q64">
         <v>324.37</v>
@@ -9368,7 +9368,7 @@
         <v>63</v>
       </c>
       <c r="P65">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="Q65">
         <v>16863.2</v>
@@ -9484,7 +9484,7 @@
         <v>14</v>
       </c>
       <c r="P66">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="Q66">
         <v>771.23</v>
@@ -9600,7 +9600,7 @@
         <v>57</v>
       </c>
       <c r="P67">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="Q67">
         <v>168.93</v>
@@ -9716,7 +9716,7 @@
         <v>80</v>
       </c>
       <c r="P68">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="Q68">
         <v>2274.7</v>
@@ -9832,7 +9832,7 @@
         <v>48</v>
       </c>
       <c r="P69">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="Q69">
         <v>91.42</v>
@@ -9948,7 +9948,7 @@
         <v>4</v>
       </c>
       <c r="P70">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="Q70">
         <v>1844.52</v>
@@ -10064,7 +10064,7 @@
         <v>17</v>
       </c>
       <c r="P71">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="Q71">
         <v>860.11</v>
@@ -10180,7 +10180,7 @@
         <v>8</v>
       </c>
       <c r="P72">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="Q72">
         <v>1574.82</v>
@@ -10296,7 +10296,7 @@
         <v>51</v>
       </c>
       <c r="P73">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="Q73">
         <v>2921.78</v>
@@ -10412,7 +10412,7 @@
         <v>85</v>
       </c>
       <c r="P74">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="Q74">
         <v>4240.66</v>
@@ -10644,7 +10644,7 @@
         <v>16</v>
       </c>
       <c r="P76">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="Q76">
         <v>1045.88</v>
@@ -10760,7 +10760,7 @@
         <v>58</v>
       </c>
       <c r="P77">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="Q77">
         <v>1196.98</v>
@@ -10876,7 +10876,7 @@
         <v>23</v>
       </c>
       <c r="P78">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Q78">
         <v>2304.14</v>
@@ -10992,7 +10992,7 @@
         <v>22</v>
       </c>
       <c r="P79">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="Q79">
         <v>703.7</v>
@@ -11108,7 +11108,7 @@
         <v>36</v>
       </c>
       <c r="P80">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="Q80">
         <v>544.4299999999999</v>
@@ -11224,7 +11224,7 @@
         <v>49</v>
       </c>
       <c r="P81">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="Q81">
         <v>4984.1</v>
@@ -11340,7 +11340,7 @@
         <v>72</v>
       </c>
       <c r="P82">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Q82">
         <v>916.05</v>
@@ -11456,7 +11456,7 @@
         <v>15</v>
       </c>
       <c r="P83">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="Q83">
         <v>337.82</v>
@@ -11688,7 +11688,7 @@
         <v>79</v>
       </c>
       <c r="P85">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="Q85">
         <v>548.97</v>
@@ -12036,7 +12036,7 @@
         <v>54</v>
       </c>
       <c r="P88">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="Q88">
         <v>1620.5</v>
@@ -12152,7 +12152,7 @@
         <v>29</v>
       </c>
       <c r="P89">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="Q89">
         <v>457.89</v>
@@ -12268,7 +12268,7 @@
         <v>92</v>
       </c>
       <c r="P90">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="Q90">
         <v>12.99</v>
@@ -12384,7 +12384,7 @@
         <v>75</v>
       </c>
       <c r="P91">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="Q91">
         <v>80.26000000000001</v>
@@ -12616,7 +12616,7 @@
         <v>62</v>
       </c>
       <c r="P93">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="Q93">
         <v>723.92</v>
@@ -12732,7 +12732,7 @@
         <v>74</v>
       </c>
       <c r="P94">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="Q94">
         <v>817.78</v>
@@ -12848,7 +12848,7 @@
         <v>38</v>
       </c>
       <c r="P95">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="Q95">
         <v>4924.32</v>
@@ -13080,7 +13080,7 @@
         <v>71</v>
       </c>
       <c r="P97">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="Q97">
         <v>381.64</v>
@@ -13196,7 +13196,7 @@
         <v>27</v>
       </c>
       <c r="P98">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q98">
         <v>1009.35</v>
@@ -13312,7 +13312,7 @@
         <v>3</v>
       </c>
       <c r="P99">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Q99">
         <v>66.54000000000001</v>
@@ -13428,7 +13428,7 @@
         <v>36</v>
       </c>
       <c r="P100">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="Q100">
         <v>128.94</v>
@@ -13544,7 +13544,7 @@
         <v>13</v>
       </c>
       <c r="P101">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="Q101">
         <v>106.71</v>
@@ -13660,7 +13660,7 @@
         <v>8</v>
       </c>
       <c r="P102">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="Q102">
         <v>75.75</v>
@@ -13776,7 +13776,7 @@
         <v>26</v>
       </c>
       <c r="P103">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="Q103">
         <v>264.46</v>
@@ -13892,7 +13892,7 @@
         <v>53</v>
       </c>
       <c r="P104">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="Q104">
         <v>1054.18</v>
@@ -14008,7 +14008,7 @@
         <v>17</v>
       </c>
       <c r="P105">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Q105">
         <v>214.39</v>
@@ -14124,7 +14124,7 @@
         <v>24</v>
       </c>
       <c r="P106">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="Q106">
         <v>480.26</v>
@@ -14240,7 +14240,7 @@
         <v>56</v>
       </c>
       <c r="P107">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="Q107">
         <v>1213.62</v>
@@ -14356,7 +14356,7 @@
         <v>21</v>
       </c>
       <c r="P108">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="Q108">
         <v>441.28</v>
@@ -14472,7 +14472,7 @@
         <v>87</v>
       </c>
       <c r="P109">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="Q109">
         <v>556.3</v>
@@ -14588,7 +14588,7 @@
         <v>7</v>
       </c>
       <c r="P110">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Q110">
         <v>3332.36</v>
@@ -14704,7 +14704,7 @@
         <v>68</v>
       </c>
       <c r="P111">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="Q111">
         <v>4607.66</v>
@@ -14820,7 +14820,7 @@
         <v>31</v>
       </c>
       <c r="P112">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="Q112">
         <v>853.97</v>
@@ -14936,7 +14936,7 @@
         <v>85</v>
       </c>
       <c r="P113">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="Q113">
         <v>432.78</v>
@@ -15284,7 +15284,7 @@
         <v>64</v>
       </c>
       <c r="P116">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="Q116">
         <v>522.21</v>
@@ -15400,7 +15400,7 @@
         <v>37</v>
       </c>
       <c r="P117">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="Q117">
         <v>387.7</v>
@@ -15516,7 +15516,7 @@
         <v>42</v>
       </c>
       <c r="P118">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="Q118">
         <v>1101.58</v>
@@ -15632,7 +15632,7 @@
         <v>57</v>
       </c>
       <c r="P119">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="Q119">
         <v>3709.98</v>
@@ -15748,7 +15748,7 @@
         <v>40</v>
       </c>
       <c r="P120">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="Q120">
         <v>261.4</v>
@@ -15864,7 +15864,7 @@
         <v>40</v>
       </c>
       <c r="P121">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="Q121">
         <v>3979.22</v>
@@ -15980,7 +15980,7 @@
         <v>41</v>
       </c>
       <c r="P122">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="Q122">
         <v>1989.32</v>
@@ -16212,7 +16212,7 @@
         <v>68</v>
       </c>
       <c r="P124">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="Q124">
         <v>309.75</v>
@@ -16328,7 +16328,7 @@
         <v>59</v>
       </c>
       <c r="P125">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="Q125">
         <v>2445.5</v>
@@ -16444,7 +16444,7 @@
         <v>69</v>
       </c>
       <c r="P126">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="Q126">
         <v>786.96</v>
@@ -16560,7 +16560,7 @@
         <v>13</v>
       </c>
       <c r="P127">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="Q127">
         <v>11451</v>
@@ -16676,7 +16676,7 @@
         <v>15</v>
       </c>
       <c r="P128">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Q128">
         <v>896.9400000000001</v>
@@ -17024,7 +17024,7 @@
         <v>18</v>
       </c>
       <c r="P131">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="Q131">
         <v>1337.24</v>
@@ -17140,7 +17140,7 @@
         <v>94</v>
       </c>
       <c r="P132">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="Q132">
         <v>156.36</v>
@@ -17372,7 +17372,7 @@
         <v>51</v>
       </c>
       <c r="P134">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="Q134">
         <v>2309.5</v>
@@ -17488,7 +17488,7 @@
         <v>23</v>
       </c>
       <c r="P135">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="Q135">
         <v>2648.22</v>
@@ -17604,7 +17604,7 @@
         <v>71</v>
       </c>
       <c r="P136">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="Q136">
         <v>1053.22</v>
@@ -17836,7 +17836,7 @@
         <v>52</v>
       </c>
       <c r="P138">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="Q138">
         <v>1213.96</v>
@@ -17952,7 +17952,7 @@
         <v>6</v>
       </c>
       <c r="P139">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Q139">
         <v>75.69</v>
@@ -18184,7 +18184,7 @@
         <v>41</v>
       </c>
       <c r="P141">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="Q141">
         <v>72.45</v>
@@ -18300,7 +18300,7 @@
         <v>39</v>
       </c>
       <c r="P142">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="Q142">
         <v>72.68000000000001</v>
@@ -18416,7 +18416,7 @@
         <v>46</v>
       </c>
       <c r="P143">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="Q143">
         <v>316.34</v>
@@ -18532,7 +18532,7 @@
         <v>84</v>
       </c>
       <c r="P144">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="Q144">
         <v>1797.46</v>
@@ -18648,7 +18648,7 @@
         <v>93</v>
       </c>
       <c r="P145">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Q145">
         <v>338.86</v>
@@ -18764,7 +18764,7 @@
         <v>56</v>
       </c>
       <c r="P146">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="Q146">
         <v>1720.22</v>
@@ -18880,7 +18880,7 @@
         <v>74</v>
       </c>
       <c r="P147">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="Q147">
         <v>10487.6</v>
@@ -18996,7 +18996,7 @@
         <v>77</v>
       </c>
       <c r="P148">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="Q148">
         <v>447.72</v>
@@ -19112,7 +19112,7 @@
         <v>46</v>
       </c>
       <c r="P149">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="Q149">
         <v>222.41</v>
@@ -19228,7 +19228,7 @@
         <v>48</v>
       </c>
       <c r="P150">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="Q150">
         <v>37266</v>
@@ -19344,7 +19344,7 @@
         <v>14</v>
       </c>
       <c r="P151">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="Q151">
         <v>359.02</v>
@@ -19460,7 +19460,7 @@
         <v>94</v>
       </c>
       <c r="P152">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="Q152">
         <v>1677.5</v>
@@ -19576,7 +19576,7 @@
         <v>89</v>
       </c>
       <c r="P153">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="Q153">
         <v>5559.2</v>
@@ -20040,7 +20040,7 @@
         <v>65</v>
       </c>
       <c r="P157">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="Q157">
         <v>1849.66</v>
@@ -20156,7 +20156,7 @@
         <v>55</v>
       </c>
       <c r="P158">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="Q158">
         <v>1487.76</v>
@@ -20272,7 +20272,7 @@
         <v>5</v>
       </c>
       <c r="P159">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Q159">
         <v>2179.64</v>
@@ -20388,7 +20388,7 @@
         <v>84</v>
       </c>
       <c r="P160">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Q160">
         <v>114.23</v>
@@ -20852,7 +20852,7 @@
         <v>38</v>
       </c>
       <c r="P164">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="Q164">
         <v>252.21</v>
@@ -20968,7 +20968,7 @@
         <v>95</v>
       </c>
       <c r="P165">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="Q165">
         <v>31258</v>
@@ -21084,7 +21084,7 @@
         <v>24</v>
       </c>
       <c r="P166">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Q166">
         <v>897.79</v>
@@ -21200,7 +21200,7 @@
         <v>30</v>
       </c>
       <c r="P167">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="Q167">
         <v>1431.96</v>
@@ -21316,7 +21316,7 @@
         <v>96</v>
       </c>
       <c r="P168">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="Q168">
         <v>4441.84</v>
@@ -21432,7 +21432,7 @@
         <v>95</v>
       </c>
       <c r="P169">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="Q169">
         <v>412.35</v>
@@ -21548,7 +21548,7 @@
         <v>26</v>
       </c>
       <c r="P170">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="Q170">
         <v>297.91</v>
@@ -21664,7 +21664,7 @@
         <v>33</v>
       </c>
       <c r="P171">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="Q171">
         <v>1192.08</v>
@@ -21780,7 +21780,7 @@
         <v>4</v>
       </c>
       <c r="P172">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="Q172">
         <v>193.89</v>
@@ -21896,7 +21896,7 @@
         <v>88</v>
       </c>
       <c r="P173">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="Q173">
         <v>173.43</v>
@@ -22128,7 +22128,7 @@
         <v>50</v>
       </c>
       <c r="P175">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="Q175">
         <v>1710.54</v>
@@ -22244,7 +22244,7 @@
         <v>71</v>
       </c>
       <c r="P176">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="Q176">
         <v>953.97</v>
@@ -22360,7 +22360,7 @@
         <v>19</v>
       </c>
       <c r="P177">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="Q177">
         <v>21932</v>
@@ -22476,7 +22476,7 @@
         <v>88</v>
       </c>
       <c r="P178">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="Q178">
         <v>948.4299999999999</v>
@@ -22592,7 +22592,7 @@
         <v>78</v>
       </c>
       <c r="P179">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="Q179">
         <v>3716.42</v>
@@ -22708,7 +22708,7 @@
         <v>93</v>
       </c>
       <c r="P180">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q180">
         <v>19906.2</v>
@@ -22940,7 +22940,7 @@
         <v>42</v>
       </c>
       <c r="P182">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="Q182">
         <v>2478.94</v>
@@ -23172,7 +23172,7 @@
         <v>52</v>
       </c>
       <c r="P184">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="Q184">
         <v>3476.72</v>
@@ -23288,7 +23288,7 @@
         <v>3</v>
       </c>
       <c r="P185">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Q185">
         <v>38.09</v>
@@ -23404,7 +23404,7 @@
         <v>5</v>
       </c>
       <c r="P186">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Q186">
         <v>239.63</v>
@@ -23520,7 +23520,7 @@
         <v>29</v>
       </c>
       <c r="P187">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="Q187">
         <v>961.03</v>
@@ -23636,7 +23636,7 @@
         <v>8</v>
       </c>
       <c r="P188">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="Q188">
         <v>3081.3</v>
@@ -23752,7 +23752,7 @@
         <v>35</v>
       </c>
       <c r="P189">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="Q189">
         <v>345.22</v>
@@ -23868,7 +23868,7 @@
         <v>60</v>
       </c>
       <c r="P190">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="Q190">
         <v>175.65</v>
@@ -23984,7 +23984,7 @@
         <v>43</v>
       </c>
       <c r="P191">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="Q191">
         <v>2105.34</v>
@@ -24216,7 +24216,7 @@
         <v>7</v>
       </c>
       <c r="P193">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Q193">
         <v>2326.94</v>
@@ -24332,7 +24332,7 @@
         <v>85</v>
       </c>
       <c r="P194">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="Q194">
         <v>4455.3</v>
@@ -24448,7 +24448,7 @@
         <v>2</v>
       </c>
       <c r="P195">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q195">
         <v>282.07</v>
@@ -24680,7 +24680,7 @@
         <v>25</v>
       </c>
       <c r="P197">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="Q197">
         <v>2834.16</v>
@@ -24912,7 +24912,7 @@
         <v>43</v>
       </c>
       <c r="P199">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="Q199">
         <v>10671.8</v>
@@ -25144,7 +25144,7 @@
         <v>66</v>
       </c>
       <c r="P201">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="Q201">
         <v>1351.04</v>
@@ -25260,7 +25260,7 @@
         <v>34</v>
       </c>
       <c r="P202">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="Q202">
         <v>1103.76</v>
@@ -25492,7 +25492,7 @@
         <v>66</v>
       </c>
       <c r="P204">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="Q204">
         <v>438.53</v>
@@ -25608,7 +25608,7 @@
         <v>16</v>
       </c>
       <c r="P205">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="Q205">
         <v>259.83</v>
@@ -25724,7 +25724,7 @@
         <v>11</v>
       </c>
       <c r="P206">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="Q206">
         <v>98.84</v>
@@ -25840,7 +25840,7 @@
         <v>15</v>
       </c>
       <c r="P207">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q207">
         <v>1050.34</v>
@@ -25956,7 +25956,7 @@
         <v>9</v>
       </c>
       <c r="P208">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Q208">
         <v>2357.1</v>
@@ -26072,7 +26072,7 @@
         <v>22</v>
       </c>
       <c r="P209">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="Q209">
         <v>160.91</v>
@@ -26188,7 +26188,7 @@
         <v>39</v>
       </c>
       <c r="P210">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="Q210">
         <v>20.73</v>
@@ -26304,7 +26304,7 @@
         <v>78</v>
       </c>
       <c r="P211">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="Q211">
         <v>1136.2</v>
